--- a/artfynd/A 1373-2024 artfynd.xlsx
+++ b/artfynd/A 1373-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1373-2024 artfynd.xlsx
+++ b/artfynd/A 1373-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94849671</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569752.8632162299</v>
+        <v>569753</v>
       </c>
       <c r="R2" t="n">
-        <v>6425699.027331154</v>
+        <v>6425699</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,19 +750,9 @@
           <t>2021-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114572183</v>
+        <v>94848839</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,49 +791,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 1373, Hackenäs, Sm</t>
+          <t>Grundsjön-Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569678</v>
+        <v>569813</v>
       </c>
       <c r="R3" t="n">
-        <v>6425716</v>
+        <v>6425623</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,12 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2021-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,21 +862,441 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94848991</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grundsjön-Hackenäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569766</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6425623</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94848909</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grundsjön-Hackenäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>569766</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6425623</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114572183</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 1373, Hackenäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569678</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6425716</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91701012</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grundsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>569708</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6425637</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-03-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-03-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Magnus Kasselstrand, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
